--- a/history_prices/AUG/prices_11082026.xlsx
+++ b/history_prices/AUG/prices_11082026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/history_prices/AUG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_C0E7D904C248DC7F6D71B8164D5DCE3AF7CF0AB2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0DC0C6-71D1-48C6-8FBC-35A0018AA65A}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_C0E7D904C248DC7F6D71B8164D5DCE3AF7CF0AB2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC77C224-94DB-47E4-8583-9F00E0C27CEB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="530">
   <si>
     <t>ID</t>
   </si>
@@ -1604,6 +1604,12 @@
   </si>
   <si>
     <t>0451</t>
+  </si>
+  <si>
+    <t>МАЙ БЮТИ  ДЖЪРНИ ЕООД</t>
+  </si>
+  <si>
+    <t>borisovniki01@abv.bg</t>
   </si>
 </sst>
 </file>
@@ -1611,9 +1617,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1644,11 +1650,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1951,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O302"/>
+  <dimension ref="A1:O304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
@@ -12164,6 +12173,82 @@
         <v>526</v>
       </c>
     </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A303" s="4">
+        <v>452</v>
+      </c>
+      <c r="B303" t="s">
+        <v>7</v>
+      </c>
+      <c r="C303" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D303" t="s">
+        <v>528</v>
+      </c>
+      <c r="E303" t="s">
+        <v>17</v>
+      </c>
+      <c r="F303" s="2">
+        <v>0</v>
+      </c>
+      <c r="G303" s="3">
+        <v>1.6870000000000001</v>
+      </c>
+      <c r="H303" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="I303" s="2">
+        <v>1.72</v>
+      </c>
+      <c r="J303" t="s">
+        <v>18</v>
+      </c>
+      <c r="K303" t="s">
+        <v>529</v>
+      </c>
+      <c r="O303" s="4">
+        <v>206663561</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A304" s="4">
+        <v>453</v>
+      </c>
+      <c r="B304" t="s">
+        <v>7</v>
+      </c>
+      <c r="C304" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D304" t="s">
+        <v>528</v>
+      </c>
+      <c r="E304" t="s">
+        <v>22</v>
+      </c>
+      <c r="F304" s="2">
+        <v>0</v>
+      </c>
+      <c r="G304" s="3">
+        <v>1.4390000000000001</v>
+      </c>
+      <c r="H304" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="I304" s="2">
+        <v>1.48</v>
+      </c>
+      <c r="J304" t="s">
+        <v>18</v>
+      </c>
+      <c r="K304" t="s">
+        <v>529</v>
+      </c>
+      <c r="O304" s="4">
+        <v>206663561</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
